--- a/RLS-NewModelCorpRelated.xlsx
+++ b/RLS-NewModelCorpRelated.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mprasad3\Downloads\RLS-NewModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0256186c38449ae/Documents/mlj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEA97FA-BA67-410D-8A65-7ED6A5BF6625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_731C83DC6F702F37CFAE9E9EF9AE525FC9C91FE3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AC28C99-3F84-4F90-B4F7-FF0D8E1D1814}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28690" yWindow="-80" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FTE" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,8 @@
     <sheet name="RLS Detail" sheetId="7" r:id="rId7"/>
     <sheet name="Unit Distribution" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4" forceFullCalc="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" forceFullCalc="1"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -44,9 +39,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="95">
-  <si>
-    <t>TOTAL FTE Year 1</t>
-  </si>
   <si>
     <t>Year1</t>
   </si>
@@ -63,6 +55,33 @@
     <t>Year5</t>
   </si>
   <si>
+    <t>Onsite</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Onsite-FSI</t>
+  </si>
+  <si>
+    <t>Onsite-Landed</t>
+  </si>
+  <si>
+    <t>TOTAL FTE Year 1</t>
+  </si>
+  <si>
     <t>Onsite FTE (non-FSI)</t>
   </si>
   <si>
@@ -70,9 +89,6 @@
   </si>
   <si>
     <t>Onsite FTE (Landed)</t>
-  </si>
-  <si>
-    <t>Onsite</t>
   </si>
   <si>
     <t>Offshore</t>
@@ -84,34 +100,13 @@
     <t>India</t>
   </si>
   <si>
-    <t>BSA</t>
-  </si>
-  <si>
     <t>Developer</t>
-  </si>
-  <si>
-    <t>Tester</t>
   </si>
   <si>
     <t>Maintenance</t>
   </si>
   <si>
-    <t>PM</t>
-  </si>
-  <si>
     <t>Other</t>
-  </si>
-  <si>
-    <t>Lead</t>
-  </si>
-  <si>
-    <t>Dev</t>
-  </si>
-  <si>
-    <t>Onsite-FSI</t>
-  </si>
-  <si>
-    <t>Onsite-Landed</t>
   </si>
   <si>
     <t>Productivity</t>
@@ -318,16 +313,16 @@
     <t>Team</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Percentage</t>
+    <t>AMS</t>
   </si>
   <si>
     <t>HZ</t>
   </si>
   <si>
-    <t>AMS</t>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Percentage</t>
   </si>
 </sst>
 </file>
@@ -782,7 +777,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1">
         <v>39</v>
@@ -790,24 +785,24 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -827,7 +822,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4">
         <v>0</v>
@@ -847,7 +842,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B5" s="5">
         <v>7</v>
@@ -867,7 +862,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <f>B3+B4+B5</f>
@@ -892,7 +887,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6">
         <v>23</v>
@@ -912,7 +907,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <f>SUM(B6:B7)</f>
@@ -951,10 +946,10 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" s="13">
         <v>0.108253</v>
@@ -962,10 +957,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C3" s="13">
         <v>0.33145599999999997</v>
@@ -973,10 +968,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C4" s="13">
         <v>0.17644199999999999</v>
@@ -984,10 +979,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" s="13">
         <v>0.23341999999999999</v>
@@ -995,10 +990,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C6" s="13">
         <v>8.0962000000000006E-2</v>
@@ -1006,10 +1001,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="13">
         <v>6.9449999999999998E-2</v>
@@ -1037,27 +1032,27 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C3" s="10">
         <v>0</v>
@@ -1077,7 +1072,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C4" s="10">
         <v>1</v>
@@ -1097,7 +1092,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" s="10">
         <v>2</v>
@@ -1117,7 +1112,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C6" s="10">
         <v>2</v>
@@ -1132,12 +1127,12 @@
         <v>2</v>
       </c>
       <c r="G6" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="10">
         <v>1</v>
@@ -1157,10 +1152,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -1170,7 +1165,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -1180,7 +1175,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10" s="11">
         <v>0</v>
@@ -1200,7 +1195,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C11" s="11">
         <v>0</v>
@@ -1220,7 +1215,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -1230,10 +1225,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -1243,7 +1238,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C14" s="12">
         <v>1</v>
@@ -1263,7 +1258,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15" s="12">
         <v>2</v>
@@ -1283,7 +1278,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C16" s="12">
         <v>3</v>
@@ -1303,7 +1298,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17" s="12">
         <v>1</v>
@@ -1336,19 +1331,19 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1380,19 +1375,19 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1614,10 +1609,10 @@
     </row>
     <row r="26" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" ref="C26:C41" si="0">A26&amp;B26</f>
@@ -1866,10 +1861,10 @@
     </row>
     <row r="27" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="28" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -2370,262 +2365,262 @@
     </row>
     <row r="29" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
         <v>MaintenanceIndia</v>
       </c>
       <c r="D29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(D26+D27+D28+D30+D31)</f>
         <v>5</v>
       </c>
       <c r="E29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(E26+E27+E28+E30+E31)</f>
         <v>5</v>
       </c>
       <c r="F29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(F26+F27+F28+F30+F31)</f>
         <v>5</v>
       </c>
       <c r="G29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(G26+G27+G28+G30+G31)</f>
         <v>5</v>
       </c>
       <c r="H29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(H26+H27+H28+H30+H31)</f>
         <v>5</v>
       </c>
       <c r="I29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(I26+I27+I28+I30+I31)</f>
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(J26+J27+J28+J30+J31)</f>
         <v>5</v>
       </c>
       <c r="K29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(K26+K27+K28+K30+K31)</f>
         <v>5</v>
       </c>
       <c r="L29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(L26+L27+L28+L30+L31)</f>
         <v>5</v>
       </c>
       <c r="M29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(M26+M27+M28+M30+M31)</f>
         <v>5</v>
       </c>
       <c r="N29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(N26+N27+N28+N30+N31)</f>
         <v>5</v>
       </c>
       <c r="O29" s="14">
-        <f>ROUND(FTE!$B$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$B$7-(O26+O27+O28+O30+O31)</f>
         <v>5</v>
       </c>
       <c r="P29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(P26+P27+P28+P30+P31)</f>
         <v>5</v>
       </c>
       <c r="Q29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(Q26+Q27+Q28+Q30+Q31)</f>
         <v>5</v>
       </c>
       <c r="R29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(R26+R27+R28+R30+R31)</f>
         <v>5</v>
       </c>
       <c r="S29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(S26+S27+S28+S30+S31)</f>
         <v>5</v>
       </c>
       <c r="T29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(T26+T27+T28+T30+T31)</f>
         <v>5</v>
       </c>
       <c r="U29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(U26+U27+U28+U30+U31)</f>
         <v>5</v>
       </c>
       <c r="V29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(V26+V27+V28+V30+V31)</f>
         <v>5</v>
       </c>
       <c r="W29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(W26+W27+W28+W30+W31)</f>
         <v>5</v>
       </c>
       <c r="X29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(X26+X27+X28+X30+X31)</f>
         <v>5</v>
       </c>
       <c r="Y29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(Y26+Y27+Y28+Y30+Y31)</f>
         <v>5</v>
       </c>
       <c r="Z29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(Z26+Z27+Z28+Z30+Z31)</f>
         <v>5</v>
       </c>
       <c r="AA29" s="6">
-        <f>ROUND(FTE!$C$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$C$7-(AA26+AA27+AA28+AA30+AA31)</f>
         <v>5</v>
       </c>
       <c r="AB29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AB26+AB27+AB28+AB30+AB31)</f>
+        <v>4</v>
       </c>
       <c r="AC29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AC26+AC27+AC28+AC30+AC31)</f>
+        <v>4</v>
       </c>
       <c r="AD29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AD26+AD27+AD28+AD30+AD31)</f>
+        <v>4</v>
       </c>
       <c r="AE29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AE26+AE27+AE28+AE30+AE31)</f>
+        <v>4</v>
       </c>
       <c r="AF29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AF26+AF27+AF28+AF30+AF31)</f>
+        <v>4</v>
       </c>
       <c r="AG29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AG26+AG27+AG28+AG30+AG31)</f>
+        <v>4</v>
       </c>
       <c r="AH29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AH26+AH27+AH28+AH30+AH31)</f>
+        <v>4</v>
       </c>
       <c r="AI29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AI26+AI27+AI28+AI30+AI31)</f>
+        <v>4</v>
       </c>
       <c r="AJ29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AJ26+AJ27+AJ28+AJ30+AJ31)</f>
+        <v>4</v>
       </c>
       <c r="AK29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AK26+AK27+AK28+AK30+AK31)</f>
+        <v>4</v>
       </c>
       <c r="AL29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AL26+AL27+AL28+AL30+AL31)</f>
+        <v>4</v>
       </c>
       <c r="AM29" s="15">
-        <f>ROUND(FTE!$D$7*'India Role Distribution'!$C5,0)</f>
-        <v>5</v>
+        <f>FTE!$D$7-(AM26+AM27+AM28+AM30+AM31)</f>
+        <v>4</v>
       </c>
       <c r="AN29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AN26+AN27+AN28+AN30+AN31)</f>
         <v>3</v>
       </c>
       <c r="AO29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AO26+AO27+AO28+AO30+AO31)</f>
         <v>3</v>
       </c>
       <c r="AP29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AP26+AP27+AP28+AP30+AP31)</f>
         <v>3</v>
       </c>
       <c r="AQ29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AQ26+AQ27+AQ28+AQ30+AQ31)</f>
         <v>3</v>
       </c>
       <c r="AR29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AR26+AR27+AR28+AR30+AR31)</f>
         <v>3</v>
       </c>
       <c r="AS29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AS26+AS27+AS28+AS30+AS31)</f>
         <v>3</v>
       </c>
       <c r="AT29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AT26+AT27+AT28+AT30+AT31)</f>
         <v>3</v>
       </c>
       <c r="AU29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AU26+AU27+AU28+AU30+AU31)</f>
         <v>3</v>
       </c>
       <c r="AV29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AV26+AV27+AV28+AV30+AV31)</f>
         <v>3</v>
       </c>
       <c r="AW29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AW26+AW27+AW28+AW30+AW31)</f>
         <v>3</v>
       </c>
       <c r="AX29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AX26+AX27+AX28+AX30+AX31)</f>
         <v>3</v>
       </c>
       <c r="AY29" s="16">
-        <f>ROUND(FTE!$E$7*'India Role Distribution'!$C5,0)</f>
+        <f>FTE!$E$7-(AY26+AY27+AY28+AY30+AY31)</f>
         <v>3</v>
       </c>
       <c r="AZ29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(AZ26+AZ27+AZ28+AZ30+AZ31)</f>
+        <v>4</v>
       </c>
       <c r="BA29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BA26+BA27+BA28+BA30+BA31)</f>
+        <v>4</v>
       </c>
       <c r="BB29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BB26+BB27+BB28+BB30+BB31)</f>
+        <v>4</v>
       </c>
       <c r="BC29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BC26+BC27+BC28+BC30+BC31)</f>
+        <v>4</v>
       </c>
       <c r="BD29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BD26+BD27+BD28+BD30+BD31)</f>
+        <v>4</v>
       </c>
       <c r="BE29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BE26+BE27+BE28+BE30+BE31)</f>
+        <v>4</v>
       </c>
       <c r="BF29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BF26+BF27+BF28+BF30+BF31)</f>
+        <v>4</v>
       </c>
       <c r="BG29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BG26+BG27+BG28+BG30+BG31)</f>
+        <v>4</v>
       </c>
       <c r="BH29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BH26+BH27+BH28+BH30+BH31)</f>
+        <v>4</v>
       </c>
       <c r="BI29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BI26+BI27+BI28+BI30+BI31)</f>
+        <v>4</v>
       </c>
       <c r="BJ29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BJ26+BJ27+BJ28+BJ30+BJ31)</f>
+        <v>4</v>
       </c>
       <c r="BK29" s="17">
-        <f>ROUND(FTE!$F$7*'India Role Distribution'!$C5,0)</f>
-        <v>3</v>
+        <f>FTE!$F$7-(BK26+BK27+BK28+BK30+BK31)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -2874,10 +2869,10 @@
     </row>
     <row r="31" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
         <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>12</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -3126,10 +3121,10 @@
     </row>
     <row r="32" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -3378,10 +3373,10 @@
     </row>
     <row r="33" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -3581,59 +3576,59 @@
       </c>
       <c r="AZ33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BF33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BI33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK33" s="17">
         <f>VLOOKUP($A33,'Onsite Role Distribution'!$B$3:$G$7,6,FALSE)+VLOOKUP($A33,'Onsite Role Distribution'!$B$8:$G$12,6,FALSE)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -3882,10 +3877,10 @@
     </row>
     <row r="35" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -4134,10 +4129,10 @@
     </row>
     <row r="36" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -4386,10 +4381,10 @@
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -4638,10 +4633,10 @@
     </row>
     <row r="38" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -4890,10 +4885,10 @@
     </row>
     <row r="39" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -5142,10 +5137,10 @@
     </row>
     <row r="40" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -5394,10 +5389,10 @@
     </row>
     <row r="41" spans="1:63" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -5856,10 +5851,10 @@
     </row>
     <row r="3" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" ref="C3:C28" si="0">A3&amp;B3</f>
@@ -5916,14 +5911,205 @@
         <f>ROUND(VLOOKUP($C3,RLS!$C$26:$O$31,3, FALSE)*'Unit Distribution'!$B3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="14"/>
+      <c r="Q3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL3" s="14">
+        <f>ROUND(VLOOKUP($C3,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -5980,14 +6166,205 @@
         <f>ROUND(VLOOKUP($C4,RLS!$C$26:$O$31,3,FALSE)-P3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q4" s="14"/>
+      <c r="Q4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-Q3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-R3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-S3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-T3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-U3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-V3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-W3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-X3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-Y3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-Z3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-AA3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$P$31,14,FALSE)-AB3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AC3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AD3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AE3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AF3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AG3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AH3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AI3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AJ3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AK3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AL3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AM3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AB$31,26,FALSE)-AN3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AO3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AP3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AQ3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AR3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AS3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AT3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AU3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AV3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AW3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AX3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AY3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AN$31,38,FALSE)-AZ3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BA3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BB3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BC3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BD3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BE3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BF3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BG3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BH3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BI3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BJ3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BK3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL4" s="14">
+        <f>ROUND(VLOOKUP($C4,RLS!$C$26:$AZ$31,50,FALSE)-BL3,0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -6044,14 +6421,205 @@
         <f>ROUND(VLOOKUP($C5,RLS!$C$26:$O$31,3, FALSE)*'Unit Distribution'!$B3,0)</f>
         <v>2</v>
       </c>
-      <c r="Q5" s="14"/>
+      <c r="Q5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="R5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="S5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="T5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="U5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="V5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="W5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="X5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="Y5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="Z5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AA5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AB5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AC5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AD5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AF5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AG5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AH5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AI5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AJ5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AK5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AL5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AM5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AN5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AO5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL5" s="14">
+        <f>ROUND(VLOOKUP($C5,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -6108,14 +6676,205 @@
         <f>ROUND(VLOOKUP($C6,RLS!$C$26:$O$31,3,FALSE)-P5,2)</f>
         <v>6</v>
       </c>
-      <c r="Q6" s="14"/>
+      <c r="Q6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-Q5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="R6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-R5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="S6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-S5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="T6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-T5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="U6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-U5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="V6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-V5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="W6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-W5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="X6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-X5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-Y5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-Z5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AA6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-AA5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AB6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$P$31,14,FALSE)-AB5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AC5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AD6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AD5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AE6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AE5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AF6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AF5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AG6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AG5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AH6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AH5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AI6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AI5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AJ5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AK6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AK5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AL6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AL5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AM6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AM5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AN6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AB$31,26,FALSE)-AN5,0)</f>
+        <v>5</v>
+      </c>
+      <c r="AO6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AO5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AP6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AP5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AQ6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AQ5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AR6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AR5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AS6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AS5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AT6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AT5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AU6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AU5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AV6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AV5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AW6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AW5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AX6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AX5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AY6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AY5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AZ6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AN$31,38,FALSE)-AZ5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BA6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BA5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BB6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BB5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BC6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BC5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BD6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BD5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BE6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BE5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BF6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BF5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BG6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BG5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BH6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BH5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BI6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BI5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BJ6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BJ5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BK6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BK5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="BL6" s="14">
+        <f>ROUND(VLOOKUP($C6,RLS!$C$26:$AZ$31,50,FALSE)-BL5,0)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -6172,14 +6931,205 @@
         <f>ROUND(VLOOKUP($C7,RLS!$C$26:$O$31,3, FALSE)*'Unit Distribution'!$B3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q7" s="14"/>
+      <c r="Q7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL7" s="14">
+        <f>ROUND(VLOOKUP($C7,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -6236,21 +7186,212 @@
         <f>ROUND(VLOOKUP($C8,RLS!$C$26:$O$31,3,FALSE)-P7,0)</f>
         <v>3</v>
       </c>
-      <c r="Q8" s="14"/>
+      <c r="Q8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-Q7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="R8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-R7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="S8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-S7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="T8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-T7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="U8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-U7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="V8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-V7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="W8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-W7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="X8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-X7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="Y8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-Y7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="Z8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-Z7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-AA7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$P$31,14,FALSE)-AB7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AC8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AC7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AD8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AD7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AE8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AE7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AF8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AF7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AG8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AG7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AH8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AH7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AI8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AI7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AJ8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AJ7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AK8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AK7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AL8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AL7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AM8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AM7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AN8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AB$31,26,FALSE)-AN7,0)</f>
+        <v>3</v>
+      </c>
+      <c r="AO8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AO7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AP7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AQ7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AR7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AS7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AT7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AU7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AV7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AW7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AX7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AY7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AN$31,38,FALSE)-AZ7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BA7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BB7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BC7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BD7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BE7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BF7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BG7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BH7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BI7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BJ7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BK7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL8" s="14">
+        <f>ROUND(VLOOKUP($C8,RLS!$C$26:$AZ$31,50,FALSE)-BL7,0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
         <v>MaintenanceIndia</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E9" s="14">
         <f>ROUND(VLOOKUP($C9,RLS!$C$26:$O$31,3, FALSE),0)</f>
@@ -6300,21 +7441,212 @@
         <f>ROUND(VLOOKUP($C9,RLS!$C$26:$O$31,4, FALSE),0)</f>
         <v>5</v>
       </c>
-      <c r="Q9" s="14"/>
+      <c r="Q9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="R9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="S9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="T9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="U9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="V9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="W9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="X9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="AA9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="AB9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="AD9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AE9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AF9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AG9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AH9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AI9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AK9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AL9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AM9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AN9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AB$31,26,FALSE),0)-1</f>
+        <v>3</v>
+      </c>
+      <c r="AO9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AP9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AQ9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AR9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AS9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AT9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AU9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AV9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AW9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AX9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AY9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="AZ9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>3</v>
+      </c>
+      <c r="BA9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BB9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BC9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BD9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BE9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BF9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BG9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BH9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BI9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BJ9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BK9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
+      <c r="BL9" s="14">
+        <f>ROUND(VLOOKUP($C9,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
         <v>PMIndia</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="14">
         <f>ROUND(VLOOKUP($C10,RLS!$C$26:$O$31,3, FALSE),0)</f>
@@ -6364,14 +7696,205 @@
         <f>ROUND(VLOOKUP($C10,RLS!$C$26:$O$31,3, FALSE),0)</f>
         <v>2</v>
       </c>
-      <c r="Q10" s="14"/>
+      <c r="Q10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="R10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="S10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="T10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="U10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="V10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="W10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="X10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="Y10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="Z10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AA10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AB10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$P$31,14,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AC10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AD10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AE10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AF10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AG10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AH10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AI10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AJ10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AK10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AL10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AM10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AN10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AB$31,26,FALSE),0)</f>
+        <v>2</v>
+      </c>
+      <c r="AO10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AN$31,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL10" s="14">
+        <f>ROUND(VLOOKUP($C10,RLS!$C$26:$AZ$31,50,FALSE),0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -6428,17 +7951,208 @@
         <f>ROUND(VLOOKUP($C11,RLS!$C$26:$O$31,3, FALSE)*'Unit Distribution'!$B3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q11" s="14"/>
+      <c r="Q11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$P$31,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AB$31,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AN$31,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL11" s="14">
+        <f>ROUND(VLOOKUP($C11,RLS!$C$26:$AZ$31,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
       <c r="C12" t="str">
-        <f t="shared" ref="C12" si="1">A12&amp;B12</f>
+        <f t="shared" si="0"/>
         <v>LeadIndia</v>
       </c>
       <c r="D12" t="s">
@@ -6492,14 +8206,205 @@
         <f>ROUND(VLOOKUP($C12,RLS!$C$26:$O$31,3, FALSE)*'Unit Distribution'!$B4,0)</f>
         <v>1</v>
       </c>
-      <c r="Q12" s="14"/>
+      <c r="Q12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-Q11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-R11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-S11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-T11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-U11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-V11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-W11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-X11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-Y11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-Z11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-AA11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$P$31,14,FALSE)-AB11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AC11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AD11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AE11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AF11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AG11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AH11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AI11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AJ11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AK11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AL11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AM11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AB$31,26,FALSE)-AN11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AO11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AP11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AQ11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AR11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AS11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AT11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AU11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AV11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AW11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AX11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AY11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AN$31,38,FALSE)-AZ11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BA11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BB11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BC11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BD11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BE11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BF11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BG11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BH11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BI11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BJ11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BK11,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL12" s="14">
+        <f>ROUND(VLOOKUP($C12,RLS!$C$26:$AZ$31,50,FALSE)-BL11,0)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -6556,14 +8461,205 @@
         <f>ROUND(VLOOKUP($C13,RLS!$C$32:$O$36,3, FALSE)*'Unit Distribution'!$B$3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q13" s="14"/>
+      <c r="Q13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL13" s="14">
+        <f>ROUND(VLOOKUP($C13,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -6620,14 +8716,205 @@
         <f>ROUND(VLOOKUP($C14,RLS!$C$32:$O$36,3,FALSE)-P13,0)</f>
         <v>1</v>
       </c>
-      <c r="Q14" s="14"/>
+      <c r="Q14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-Q13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-R13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-S13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-T13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-U13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-V13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-W13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-X13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-Y13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-Z13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-AA13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$P$36,14,FALSE)-AB13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AC13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AD13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AE13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AF13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AG13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AH13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AI13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AJ13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AK13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AL13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AM13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AB$36,26,FALSE)-AN13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AO13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AP13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AQ13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AR13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AS13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AT13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AU13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AV13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AW13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AX13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AY13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AN$36,38,FALSE)-AZ13,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BA13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BB13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BC13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BD13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BE13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BF13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BG13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BH13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BI13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BJ13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BK13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL14" s="14">
+        <f>ROUND(VLOOKUP($C14,RLS!$C$32:$AZ$36,50,FALSE)-BL13,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -6684,14 +8971,205 @@
         <f>ROUND(VLOOKUP($C15,RLS!$C$32:$O$36,3, FALSE)*'Unit Distribution'!$B$3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q15" s="14"/>
+      <c r="Q15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL15" s="14">
+        <f>ROUND(VLOOKUP($C15,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -6748,14 +9226,205 @@
         <f>ROUND(VLOOKUP($C16,RLS!$C$32:$O$36,3,FALSE)-P15,0)</f>
         <v>1</v>
       </c>
-      <c r="Q16" s="14"/>
+      <c r="Q16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-Q15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-R15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-S15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-T15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-U15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-V15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-W15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-X15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-Y15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-Z15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-AA15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$P$36,14,FALSE)-AB15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AC15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AD15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AE15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AF15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AG15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AH15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AI15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AJ15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AK15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AL15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AM15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AB$36,26,FALSE)-AN15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AO15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AP16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AP15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AQ16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AQ15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AR16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AR15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AS16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AS15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AT16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AT15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AU16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AU15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AV16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AV15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AW16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AW15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AX16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AX15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AY16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AY15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="AZ16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AN$36,38,FALSE)-AZ15,0)</f>
+        <v>2</v>
+      </c>
+      <c r="BA16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BA15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BB15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BC15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BD15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BE15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BF15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BG15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BH15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BI15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BJ15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BK15,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL16" s="14">
+        <f>ROUND(VLOOKUP($C16,RLS!$C$32:$AZ$36,50,FALSE)-BL15,0)</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -6812,14 +9481,205 @@
         <f>ROUND(VLOOKUP($C17,RLS!$C$32:$O$36,3, FALSE)*'Unit Distribution'!$B$3,0)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="14"/>
+      <c r="Q17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$P$36,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AB$36,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AN$36,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL17" s="14">
+        <f>ROUND(VLOOKUP($C17,RLS!$C$32:$AZ$36,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -6876,21 +9736,212 @@
         <f>ROUND(VLOOKUP($C18,RLS!$C$32:$O$36,3,FALSE)-P17,0)</f>
         <v>1</v>
       </c>
-      <c r="Q18" s="14"/>
+      <c r="Q18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-Q17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-R17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-S17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-T17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-U17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-V17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-W17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-X17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-Y17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-Z17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-AA17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$P$36,14,FALSE)-AB17,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AC17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AD17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AE17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AF17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AG17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AH17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AI17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AJ17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AK17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AL17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AM17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AB$36,26,FALSE)-AN17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AO17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AP17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AQ17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AR17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AS17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AT17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AU17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AV17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AW17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AX17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AY17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AN$36,38,FALSE)-AZ17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BA17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BB17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BC17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BD17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BE17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BF17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BG17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BH17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BI17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BJ17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BK17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL18" s="14">
+        <f>ROUND(VLOOKUP($C18,RLS!$C$32:$AZ$36,50,FALSE)-BL17,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
         <v>PMOnsite</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="14">
         <f>ROUND(VLOOKUP($C19,RLS!$C$32:$O$36,3, FALSE),0)</f>
@@ -6940,14 +9991,205 @@
         <f>ROUND(VLOOKUP($C19,RLS!$C$32:$O$36,3, FALSE),2)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="14"/>
+      <c r="Q19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="W19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL19" s="14">
+        <f>ROUND(VLOOKUP($C19,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -7001,14 +10243,205 @@
         <f>ROUND(VLOOKUP($C20,RLS!$C$32:$O$36,3, FALSE),2)</f>
         <v>1</v>
       </c>
-      <c r="Q20" s="14"/>
+      <c r="Q20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="R20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="S20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="T20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="U20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="V20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="W20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="X20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$P$36,14,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AB$36,26,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AN$36,38,FALSE),0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL20" s="14">
+        <f>ROUND(VLOOKUP($C20,RLS!$C$32:$AZ$36,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -7065,14 +10498,205 @@
         <f>ROUND(VLOOKUP($C21,RLS!$C$37:$O$41,3, FALSE)*'Unit Distribution'!$B$3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q21" s="14"/>
+      <c r="Q21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL21" s="14">
+        <f>ROUND(VLOOKUP($C21,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -7129,14 +10753,205 @@
         <f>ROUND(VLOOKUP($C22,RLS!$C$37:$O$41,3,FALSE)-P21,0)</f>
         <v>1</v>
       </c>
-      <c r="Q22" s="14"/>
+      <c r="Q22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-Q21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-R21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-S21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-T21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-U21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-V21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-W21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-X21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-Y21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-Z21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-AA21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$P$41,14,FALSE)-AB21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AC21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AD21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AE21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AF21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AG21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AH21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AI21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AJ21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AK21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AL21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AM21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AB$41,26,FALSE)-AN21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AO21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AP21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AQ21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AR21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AS21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AT21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AU21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AV21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AW21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AX21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AY21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AN$41,38,FALSE)-AZ21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BA21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BB21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BC21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BD21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BE21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BF21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BG21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BH21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BI21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BJ21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BK21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL22" s="14">
+        <f>ROUND(VLOOKUP($C22,RLS!$C$37:$AZ$41,50,FALSE)-BL21,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -7193,14 +11008,205 @@
         <f>ROUND(VLOOKUP($C23,RLS!$C$37:$O$41,3, FALSE)*'Unit Distribution'!$B$3,0)</f>
         <v>1</v>
       </c>
-      <c r="Q23" s="14"/>
+      <c r="Q23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL23" s="14">
+        <f>ROUND(VLOOKUP($C23,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -7257,14 +11263,205 @@
         <f>ROUND(VLOOKUP($C24,RLS!$C$37:$O$41,3,FALSE)-P23,0)</f>
         <v>2</v>
       </c>
-      <c r="Q24" s="14"/>
+      <c r="Q24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-Q23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-R23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-S23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-T23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-U23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-V23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-W23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-X23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-Y23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-Z23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-AA23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$P$41,14,FALSE)-AB23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AC23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AD23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AE23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AF23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AG23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AH23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AI23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AJ23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AK23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AL23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AM23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AB$41,26,FALSE)-AN23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AO23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AP23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AQ23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AR23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AS23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AT23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AU23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AV23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AW23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AX23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AY23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AN$41,38,FALSE)-AZ23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BA23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BB23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BC23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BD23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BE23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BF23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BG23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BH23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BI23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BJ23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BK23,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL24" s="14">
+        <f>ROUND(VLOOKUP($C24,RLS!$C$37:$AZ$41,50,FALSE)-BL23,0)</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -7321,14 +11518,205 @@
         <f>ROUND(VLOOKUP($C25,RLS!$C$37:$O$41,3, FALSE)*'Unit Distribution'!$B$3,0)</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="14"/>
+      <c r="Q25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$P$41,14,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AB$41,26,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AN$41,38,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL25" s="14">
+        <f>ROUND(VLOOKUP($C25,RLS!$C$37:$AZ$41,50,FALSE)*'Unit Distribution'!$B$3,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -7385,14 +11773,205 @@
         <f>ROUND(VLOOKUP($C26,RLS!$C$37:$O$41,3,FALSE)-P25,0)</f>
         <v>1</v>
       </c>
-      <c r="Q26" s="14"/>
+      <c r="Q26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-Q25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-R25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-S25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-T25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-U25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="V26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-V25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-W25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="X26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-X25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Y26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-Y25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Z26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-Z25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AA26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-AA25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AB26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$P$41,14,FALSE)-AB25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AC26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AC25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AD26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AD25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AE26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AE25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AF26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AF25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AG26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AG25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AH26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AH25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AI26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AI25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AJ25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AK26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AK25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AL26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AL25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AM26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AM25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AN26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AB$41,26,FALSE)-AN25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AO26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AO25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AP26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AP25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AQ25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AR26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AR25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AS26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AS25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AT26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AT25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AU26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AU25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AV25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AW26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AW25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AX26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AX25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AY26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AY25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AN$41,38,FALSE)-AZ25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BA26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BA25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BB25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BC26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BC25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BD26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BD25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BE25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BF25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BG25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BH26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BH25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BI25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BJ25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BK26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BK25,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BL26" s="14">
+        <f>ROUND(VLOOKUP($C26,RLS!$C$37:$AZ$41,50,FALSE)-BL25,0)</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -7446,14 +12025,205 @@
         <f>ROUND(VLOOKUP($C27,RLS!$C$37:$O$41,3, FALSE),0)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="14"/>
+      <c r="Q27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="W27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL27" s="14">
+        <f>ROUND(VLOOKUP($C27,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -7510,7 +12280,198 @@
         <f>ROUND(VLOOKUP($C28,RLS!$C$37:$O$41,3, FALSE),0)</f>
         <v>1</v>
       </c>
-      <c r="Q28" s="14"/>
+      <c r="Q28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="R28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="T28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="U28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="V28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="W28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="X28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$P$41,14,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AK28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AL28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AB$41,26,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AN$41,38,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BK28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BL28" s="14">
+        <f>ROUND(VLOOKUP($C28,RLS!$C$37:$AZ$41,50,FALSE),0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7524,10 +12485,10 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -7549,10 +12510,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{bb5d96ea-ab39-44a0-a6d6-b6f0aac5958b}" enabled="1" method="Standard" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>